--- a/output/tables/table3_summary_stats.xlsx
+++ b/output/tables/table3_summary_stats.xlsx
@@ -45,7 +45,7 @@
     <t>delta_log_salary</t>
   </si>
   <si>
-    <t>ai_exposure</t>
+    <t>m1</t>
   </si>
   <si>
     <t>salary</t>
